--- a/salidas/empresas/TJX.xlsx
+++ b/salidas/empresas/TJX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>4.859379768371582</v>
+        <v>4.859377861022949</v>
       </c>
       <c r="C2" t="n">
         <v>6.382500171661377</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>4.672566413879395</v>
+        <v>4.672567844390869</v>
       </c>
       <c r="C3" t="n">
         <v>6.122499942779541</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>4.735528469085693</v>
+        <v>4.735528945922852</v>
       </c>
       <c r="C4" t="n">
         <v>6.204999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.6038818359375</v>
+        <v>4.603882312774658</v>
       </c>
       <c r="C5" t="n">
         <v>6.03249979019165</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>4.536667823791504</v>
+        <v>4.536666393280029</v>
       </c>
       <c r="C6" t="n">
         <v>5.927499771118164</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>4.374029636383057</v>
+        <v>4.37402868270874</v>
       </c>
       <c r="C7" t="n">
         <v>5.715000152587891</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>4.662952899932861</v>
+        <v>4.662955284118652</v>
       </c>
       <c r="C8" t="n">
         <v>6.09250020980835</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>5.132264137268066</v>
+        <v>5.132265090942383</v>
       </c>
       <c r="C9" t="n">
         <v>6.6875</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>5.377846717834473</v>
+        <v>5.377847194671631</v>
       </c>
       <c r="C10" t="n">
         <v>7.007500171661377</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>5.55435848236084</v>
+        <v>5.554358005523682</v>
       </c>
       <c r="C11" t="n">
         <v>7.237500190734863</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>5.273448944091797</v>
+        <v>5.273449420928955</v>
       </c>
       <c r="C12" t="n">
         <v>6.855000019073486</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>5.485002040863037</v>
+        <v>5.485001564025879</v>
       </c>
       <c r="C13" t="n">
         <v>7.130000114440918</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>5.686940670013428</v>
+        <v>5.686939239501953</v>
       </c>
       <c r="C14" t="n">
         <v>7.392499923706055</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>5.302038669586182</v>
+        <v>5.302038192749023</v>
       </c>
       <c r="C15" t="n">
         <v>6.875</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>5.19792652130127</v>
+        <v>5.197924613952637</v>
       </c>
       <c r="C16" t="n">
         <v>6.739999771118164</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>5.377231597900391</v>
+        <v>5.377232074737549</v>
       </c>
       <c r="C17" t="n">
         <v>6.972499847412109</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>5.409903049468994</v>
+        <v>5.409901142120361</v>
       </c>
       <c r="C18" t="n">
         <v>6.992499828338623</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>5.318995952606201</v>
+        <v>5.318996429443359</v>
       </c>
       <c r="C19" t="n">
         <v>6.875</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>5.367350578308105</v>
+        <v>5.367351055145264</v>
       </c>
       <c r="C20" t="n">
         <v>6.9375</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>5.91614294052124</v>
+        <v>5.916142463684082</v>
       </c>
       <c r="C21" t="n">
         <v>7.622499942779541</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>5.640612125396729</v>
+        <v>5.640609741210938</v>
       </c>
       <c r="C22" t="n">
         <v>7.267499923706055</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>5.613449096679688</v>
+        <v>5.613448619842529</v>
       </c>
       <c r="C23" t="n">
         <v>7.232500076293945</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>6.153653144836426</v>
+        <v>6.153653621673584</v>
       </c>
       <c r="C26" t="n">
         <v>7.902500152587891</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>6.247461318969727</v>
+        <v>6.247459411621094</v>
       </c>
       <c r="C27" t="n">
         <v>8</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>6.290412902832031</v>
+        <v>6.290413856506348</v>
       </c>
       <c r="C29" t="n">
         <v>8.055000305175781</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>6.281145095825195</v>
+        <v>6.281141757965088</v>
       </c>
       <c r="C30" t="n">
         <v>8.015000343322754</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>6.165551662445068</v>
+        <v>6.165550708770752</v>
       </c>
       <c r="C31" t="n">
         <v>7.867499828338623</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>7.123480319976807</v>
+        <v>7.123486042022705</v>
       </c>
       <c r="C33" t="n">
         <v>9.060000419616699</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>5.999131679534912</v>
+        <v>5.999131202697754</v>
       </c>
       <c r="C34" t="n">
         <v>7.630000114440918</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.260053634643555</v>
+        <v>5.26005220413208</v>
       </c>
       <c r="C35" t="n">
         <v>6.690000057220459</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>4.060502529144287</v>
+        <v>4.060499668121338</v>
       </c>
       <c r="C37" t="n">
         <v>5.142499923706055</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>3.833490610122681</v>
+        <v>3.833489894866943</v>
       </c>
       <c r="C38" t="n">
         <v>4.855000019073486</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>4.417677402496338</v>
+        <v>4.417678833007812</v>
       </c>
       <c r="C39" t="n">
         <v>5.567500114440918</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>5.086182594299316</v>
+        <v>5.086181640625</v>
       </c>
       <c r="C40" t="n">
         <v>6.409999847412109</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.548381805419922</v>
+        <v>5.548378944396973</v>
       </c>
       <c r="C41" t="n">
         <v>6.992499828338623</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>5.879199981689453</v>
+        <v>5.87920093536377</v>
       </c>
       <c r="C42" t="n">
         <v>7.377500057220459</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>7.218008041381836</v>
+        <v>7.218009948730469</v>
       </c>
       <c r="C44" t="n">
         <v>9.057499885559082</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.186748027801514</v>
+        <v>7.186747550964355</v>
       </c>
       <c r="C45" t="n">
         <v>8.987500190734863</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.426639080047607</v>
+        <v>7.426637172698975</v>
       </c>
       <c r="C46" t="n">
         <v>9.287500381469727</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.466618061065674</v>
+        <v>7.466619491577148</v>
       </c>
       <c r="C47" t="n">
         <v>9.337499618530273</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.696620464324951</v>
+        <v>7.696622848510742</v>
       </c>
       <c r="C48" t="n">
         <v>9.595000267028809</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>7.329641342163086</v>
+        <v>7.329638481140137</v>
       </c>
       <c r="C49" t="n">
         <v>9.137499809265137</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.622424602508545</v>
+        <v>7.622422695159912</v>
       </c>
       <c r="C50" t="n">
         <v>9.502499580383301</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.374963760375977</v>
+        <v>8.374961853027344</v>
       </c>
       <c r="C51" t="n">
         <v>10.40750026702881</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>8.554009437561035</v>
+        <v>8.554008483886719</v>
       </c>
       <c r="C52" t="n">
         <v>10.63000011444092</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>9.175540924072266</v>
+        <v>9.175545692443848</v>
       </c>
       <c r="C54" t="n">
         <v>11.36499977111816</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>8.467097282409668</v>
+        <v>8.467098236083984</v>
       </c>
       <c r="C55" t="n">
         <v>10.48750019073486</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.380306243896484</v>
+        <v>8.380302429199219</v>
       </c>
       <c r="C56" t="n">
         <v>10.38000011444092</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.038999557495117</v>
+        <v>8.038998603820801</v>
       </c>
       <c r="C57" t="n">
         <v>9.922499656677246</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.039569854736328</v>
+        <v>9.039568901062012</v>
       </c>
       <c r="C58" t="n">
         <v>11.15750026702881</v>
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.267585754394531</v>
+        <v>9.267580986022949</v>
       </c>
       <c r="C60" t="n">
         <v>11.40250015258789</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>9.019687652587891</v>
+        <v>9.019686698913574</v>
       </c>
       <c r="C61" t="n">
         <v>11.09749984741211</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>9.62926197052002</v>
+        <v>9.629262924194336</v>
       </c>
       <c r="C62" t="n">
         <v>11.84749984741211</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>10.16380214691162</v>
+        <v>10.16379928588867</v>
       </c>
       <c r="C63" t="n">
         <v>12.46749973297119</v>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.13526821136475</v>
+        <v>10.1352653503418</v>
       </c>
       <c r="C64" t="n">
         <v>12.43249988555908</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.92807197570801</v>
+        <v>10.92806911468506</v>
       </c>
       <c r="C65" t="n">
         <v>13.40499973297119</v>
@@ -1832,11 +1844,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.84454822540283</v>
+        <v>10.84455013275146</v>
       </c>
       <c r="C66" t="n">
         <v>13.25500011444092</v>
@@ -1861,11 +1873,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.74432563781738</v>
+        <v>10.7443265914917</v>
       </c>
       <c r="C67" t="n">
         <v>13.13249969482422</v>
@@ -1890,11 +1902,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>11.31089401245117</v>
+        <v>11.31088829040527</v>
       </c>
       <c r="C68" t="n">
         <v>13.82499980926514</v>
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.21377277374268</v>
+        <v>11.21377372741699</v>
       </c>
       <c r="C69" t="n">
         <v>13.65499973297119</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>11.38828468322754</v>
+        <v>11.38828086853027</v>
       </c>
       <c r="C70" t="n">
         <v>13.86750030517578</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.09863758087158</v>
+        <v>12.09863567352295</v>
       </c>
       <c r="C71" t="n">
         <v>14.73250007629395</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.70718860626221</v>
+        <v>12.70719051361084</v>
       </c>
       <c r="C72" t="n">
         <v>15.42500019073486</v>
@@ -2035,7 +2047,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>14.03351497650146</v>
+        <v>14.0335168838501</v>
       </c>
       <c r="C74" t="n">
         <v>17.03499984741211</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>15.12160873413086</v>
+        <v>15.12160491943359</v>
       </c>
       <c r="C75" t="n">
         <v>18.30500030517578</v>
@@ -2122,7 +2134,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2151,11 +2163,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>17.22813987731934</v>
+        <v>17.22813606262207</v>
       </c>
       <c r="C77" t="n">
         <v>20.85499954223633</v>
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.58666610717773</v>
+        <v>17.58666801452637</v>
       </c>
       <c r="C78" t="n">
         <v>21.22999954223633</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.78133964538574</v>
+        <v>17.78134536743164</v>
       </c>
       <c r="C79" t="n">
         <v>21.46500015258789</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.34050178527832</v>
+        <v>18.34049987792969</v>
       </c>
       <c r="C80" t="n">
         <v>22.13999938964844</v>
@@ -2267,7 +2279,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>18.59901237487793</v>
+        <v>18.59900665283203</v>
       </c>
       <c r="C82" t="n">
         <v>22.39500045776367</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.28680801391602</v>
+        <v>17.28682136535645</v>
       </c>
       <c r="C83" t="n">
         <v>20.81500053405762</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>18.46271896362305</v>
+        <v>18.46271133422852</v>
       </c>
       <c r="C84" t="n">
         <v>22.17000007629395</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.67573165893555</v>
+        <v>17.67572975158691</v>
       </c>
       <c r="C85" t="n">
         <v>21.22500038146973</v>
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>18.81247520446777</v>
+        <v>18.81247711181641</v>
       </c>
       <c r="C86" t="n">
         <v>22.59000015258789</v>
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.77258110046387</v>
+        <v>18.77259254455566</v>
       </c>
       <c r="C87" t="n">
         <v>22.48500061035156</v>
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>19.51564407348633</v>
+        <v>19.51564025878906</v>
       </c>
       <c r="C88" t="n">
         <v>23.375</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.35887718200684</v>
+        <v>20.35888290405273</v>
       </c>
       <c r="C89" t="n">
         <v>24.38500022888184</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>21.18764305114746</v>
+        <v>21.1876335144043</v>
       </c>
       <c r="C90" t="n">
         <v>25.30500030517578</v>
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>20.95738983154297</v>
+        <v>20.95739364624023</v>
       </c>
       <c r="C91" t="n">
         <v>25.03000068664551</v>
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>21.78630447387695</v>
+        <v>21.78630065917969</v>
       </c>
       <c r="C92" t="n">
         <v>26.02000045776367</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>22.13222885131836</v>
+        <v>22.13222694396973</v>
       </c>
       <c r="C93" t="n">
         <v>26.36000061035156</v>
@@ -2644,7 +2656,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>25.52007102966309</v>
+        <v>25.52006912231445</v>
       </c>
       <c r="C95" t="n">
         <v>30.39500045776367</v>
@@ -2702,11 +2714,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>26.45966148376465</v>
+        <v>26.45966339111328</v>
       </c>
       <c r="C96" t="n">
         <v>31.44000053405762</v>
@@ -2731,11 +2743,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>26.81733512878418</v>
+        <v>26.81733894348145</v>
       </c>
       <c r="C97" t="n">
         <v>31.86499977111816</v>
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>24.13686370849609</v>
+        <v>24.13686943054199</v>
       </c>
       <c r="C98" t="n">
         <v>28.68000030517578</v>
@@ -2789,11 +2801,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>25.92557334899902</v>
+        <v>25.92555999755859</v>
       </c>
       <c r="C99" t="n">
         <v>30.72999954223633</v>
@@ -2818,11 +2830,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>25.58388328552246</v>
+        <v>25.58388137817383</v>
       </c>
       <c r="C100" t="n">
         <v>30.32500076293945</v>
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>24.54196357727051</v>
+        <v>24.54197120666504</v>
       </c>
       <c r="C101" t="n">
         <v>29.09000015258789</v>
@@ -2876,7 +2888,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>22.48591041564941</v>
+        <v>22.48591613769531</v>
       </c>
       <c r="C103" t="n">
         <v>26.57500076293945</v>
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>25.30021095275879</v>
+        <v>25.30021286010742</v>
       </c>
       <c r="C105" t="n">
         <v>29.80500030517578</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>25.11346626281738</v>
+        <v>25.11346435546875</v>
       </c>
       <c r="C106" t="n">
         <v>29.58499908447266</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>26.87483787536621</v>
+        <v>26.87483978271484</v>
       </c>
       <c r="C107" t="n">
         <v>31.65999984741211</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>28.15721702575684</v>
+        <v>28.15720748901367</v>
       </c>
       <c r="C108" t="n">
         <v>33.08000183105469</v>
@@ -3079,7 +3091,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3108,7 +3120,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.28861045837402</v>
+        <v>29.28861808776855</v>
       </c>
       <c r="C111" t="n">
         <v>34.31999969482422</v>
@@ -3166,11 +3178,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>29.89026069641113</v>
+        <v>29.89025497436523</v>
       </c>
       <c r="C112" t="n">
         <v>35.02500152587891</v>
@@ -3195,11 +3207,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.53914260864258</v>
+        <v>27.53915023803711</v>
       </c>
       <c r="C113" t="n">
         <v>32.27000045776367</v>
@@ -3224,11 +3236,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>27.55745315551758</v>
+        <v>27.55745506286621</v>
       </c>
       <c r="C114" t="n">
         <v>32.18999862670898</v>
@@ -3253,11 +3265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>28.32365798950195</v>
+        <v>28.32364654541016</v>
       </c>
       <c r="C115" t="n">
         <v>33.08499908447266</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>29.88601112365723</v>
+        <v>29.88601875305176</v>
       </c>
       <c r="C116" t="n">
         <v>34.90999984741211</v>
@@ -3311,11 +3323,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>30.19038200378418</v>
+        <v>30.19038391113281</v>
       </c>
       <c r="C117" t="n">
         <v>35.15999984741211</v>
@@ -3340,11 +3352,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>30.66265487670898</v>
+        <v>30.66264343261719</v>
       </c>
       <c r="C118" t="n">
         <v>35.70999908447266</v>
@@ -3369,11 +3381,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.42255783081055</v>
+        <v>31.42255020141602</v>
       </c>
       <c r="C119" t="n">
         <v>36.59500122070312</v>
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>30.39812850952148</v>
+        <v>30.39813232421875</v>
       </c>
       <c r="C120" t="n">
         <v>35.29999923706055</v>
@@ -3427,11 +3439,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>30.53161239624023</v>
+        <v>30.53160095214844</v>
       </c>
       <c r="C121" t="n">
         <v>35.45500183105469</v>
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>30.67368698120117</v>
+        <v>30.67369079589844</v>
       </c>
       <c r="C122" t="n">
         <v>35.61999893188477</v>
@@ -3485,11 +3497,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>32.00393295288086</v>
+        <v>32.00392532348633</v>
       </c>
       <c r="C123" t="n">
         <v>37.04999923706055</v>
@@ -3514,11 +3526,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>33.83951187133789</v>
+        <v>33.83950424194336</v>
       </c>
       <c r="C124" t="n">
         <v>39.17499923706055</v>
@@ -3543,11 +3555,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.74679183959961</v>
+        <v>32.74679946899414</v>
       </c>
       <c r="C125" t="n">
         <v>37.90999984741211</v>
@@ -3572,11 +3584,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.98662567138672</v>
+        <v>32.98664474487305</v>
       </c>
       <c r="C126" t="n">
         <v>38.06000137329102</v>
@@ -3601,11 +3613,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>33.46765518188477</v>
+        <v>33.46764755249023</v>
       </c>
       <c r="C127" t="n">
         <v>38.6150016784668</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.41340255737305</v>
+        <v>35.41340637207031</v>
       </c>
       <c r="C128" t="n">
         <v>40.86000061035156</v>
@@ -3659,11 +3671,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>33.66595458984375</v>
+        <v>33.66595840454102</v>
       </c>
       <c r="C129" t="n">
         <v>38.72000122070312</v>
@@ -3688,11 +3700,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>32.50956344604492</v>
+        <v>32.50955200195312</v>
       </c>
       <c r="C130" t="n">
         <v>37.38999938964844</v>
@@ -3717,11 +3729,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>32.06178283691406</v>
+        <v>32.06177139282227</v>
       </c>
       <c r="C131" t="n">
         <v>36.875</v>
@@ -3746,11 +3758,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>34.17840194702148</v>
+        <v>34.17839431762695</v>
       </c>
       <c r="C132" t="n">
         <v>39.16999816894531</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>32.77794647216797</v>
+        <v>32.77793884277344</v>
       </c>
       <c r="C133" t="n">
         <v>37.56499862670898</v>
@@ -3804,11 +3816,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>32.68632507324219</v>
+        <v>32.68630981445312</v>
       </c>
       <c r="C134" t="n">
         <v>37.45999908447266</v>
@@ -3833,11 +3845,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>34.34493637084961</v>
+        <v>34.34492492675781</v>
       </c>
       <c r="C135" t="n">
         <v>39.22499847412109</v>
@@ -3862,11 +3874,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>34.62074279785156</v>
+        <v>34.62074661254883</v>
       </c>
       <c r="C136" t="n">
         <v>39.54000091552734</v>
@@ -3891,7 +3903,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3920,11 +3932,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>33.05829238891602</v>
+        <v>33.05828857421875</v>
       </c>
       <c r="C138" t="n">
         <v>37.60499954223633</v>
@@ -3949,11 +3961,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>31.72208023071289</v>
+        <v>31.72206878662109</v>
       </c>
       <c r="C139" t="n">
         <v>36.08499908447266</v>
@@ -3978,11 +3990,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>30.90450859069824</v>
+        <v>30.90451431274414</v>
       </c>
       <c r="C140" t="n">
         <v>35.15499877929688</v>
@@ -4007,11 +4019,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.92057037353516</v>
+        <v>31.92057418823242</v>
       </c>
       <c r="C141" t="n">
         <v>36.15000152587891</v>
@@ -4036,11 +4048,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>32.55191802978516</v>
+        <v>32.55192565917969</v>
       </c>
       <c r="C142" t="n">
         <v>36.8650016784668</v>
@@ -4065,11 +4077,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>30.81681251525879</v>
+        <v>30.81682586669922</v>
       </c>
       <c r="C143" t="n">
         <v>34.90000152587891</v>
@@ -4094,7 +4106,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4123,11 +4135,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>33.91263198852539</v>
+        <v>33.91262435913086</v>
       </c>
       <c r="C145" t="n">
         <v>38.22999954223633</v>
@@ -4152,7 +4164,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4181,11 +4193,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>36.82395935058594</v>
+        <v>36.82397842407227</v>
       </c>
       <c r="C147" t="n">
         <v>41.34000015258789</v>
@@ -4210,11 +4222,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>36.32514572143555</v>
+        <v>36.32515335083008</v>
       </c>
       <c r="C148" t="n">
         <v>40.77999877929688</v>
@@ -4239,11 +4251,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>37.79044723510742</v>
+        <v>37.79045104980469</v>
       </c>
       <c r="C149" t="n">
         <v>42.42499923706055</v>
@@ -4268,11 +4280,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>40.41080093383789</v>
+        <v>40.41080474853516</v>
       </c>
       <c r="C150" t="n">
         <v>45.15999984741211</v>
@@ -4297,11 +4309,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.58525466918945</v>
+        <v>42.58525848388672</v>
       </c>
       <c r="C151" t="n">
         <v>47.59000015258789</v>
@@ -4326,11 +4338,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.51588439941406</v>
+        <v>43.51589202880859</v>
       </c>
       <c r="C152" t="n">
         <v>48.63000106811523</v>
@@ -4355,11 +4367,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>49.39329147338867</v>
+        <v>49.39329528808594</v>
       </c>
       <c r="C153" t="n">
         <v>54.98500061035156</v>
@@ -4384,11 +4396,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>50.31405639648438</v>
+        <v>50.31404876708984</v>
       </c>
       <c r="C154" t="n">
         <v>56.0099983215332</v>
@@ -4413,7 +4425,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4442,11 +4454,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>44.04197692871094</v>
+        <v>44.04196548461914</v>
       </c>
       <c r="C156" t="n">
         <v>48.84999847412109</v>
@@ -4471,11 +4483,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>40.33650207519531</v>
+        <v>40.33649444580078</v>
       </c>
       <c r="C157" t="n">
         <v>44.7400016784668</v>
@@ -4500,11 +4512,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>44.83536148071289</v>
+        <v>44.83536911010742</v>
       </c>
       <c r="C158" t="n">
         <v>49.72999954223633</v>
@@ -4529,7 +4541,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4558,11 +4570,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.16162490844727</v>
+        <v>48.16162109375</v>
       </c>
       <c r="C160" t="n">
         <v>53.20999908447266</v>
@@ -4587,11 +4599,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>49.67318344116211</v>
+        <v>49.67317581176758</v>
       </c>
       <c r="C161" t="n">
         <v>54.88000106811523</v>
@@ -4616,11 +4628,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>45.7186393737793</v>
+        <v>45.71864700317383</v>
       </c>
       <c r="C162" t="n">
         <v>50.29000091552734</v>
@@ -4645,11 +4657,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>48.07321166992188</v>
+        <v>48.07320785522461</v>
       </c>
       <c r="C163" t="n">
         <v>52.88000106811523</v>
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>49.60050201416016</v>
+        <v>49.60049819946289</v>
       </c>
       <c r="C164" t="n">
         <v>54.56000137329102</v>
@@ -4703,11 +4715,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.1888313293457</v>
+        <v>50.18883514404297</v>
       </c>
       <c r="C165" t="n">
         <v>54.97000122070312</v>
@@ -4732,7 +4744,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4761,11 +4773,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>52.6357421875</v>
+        <v>52.63573455810547</v>
       </c>
       <c r="C167" t="n">
         <v>57.65000152587891</v>
@@ -4790,11 +4802,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>56.03373336791992</v>
+        <v>56.03374099731445</v>
       </c>
       <c r="C168" t="n">
         <v>61.13000106811523</v>
@@ -4819,11 +4831,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>55.96957015991211</v>
+        <v>55.96956634521484</v>
       </c>
       <c r="C169" t="n">
         <v>61.06000137329102</v>
@@ -4848,11 +4860,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.11796951293945</v>
+        <v>54.11798095703125</v>
       </c>
       <c r="C170" t="n">
         <v>59.04000091552734</v>
@@ -4877,11 +4889,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>55.01720428466797</v>
+        <v>55.01720809936523</v>
       </c>
       <c r="C171" t="n">
         <v>59.79999923706055</v>
@@ -4906,11 +4918,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>43.98617172241211</v>
+        <v>43.98617553710938</v>
       </c>
       <c r="C172" t="n">
         <v>47.81000137329102</v>
@@ -4935,11 +4947,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>45.12699127197266</v>
+        <v>45.12698364257812</v>
       </c>
       <c r="C173" t="n">
         <v>49.04999923706055</v>
@@ -4964,7 +4976,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4993,7 +5005,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5022,7 +5034,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5051,7 +5063,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5080,11 +5092,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>51.19912719726562</v>
+        <v>51.19911956787109</v>
       </c>
       <c r="C178" t="n">
         <v>55.65000152587891</v>
@@ -5109,7 +5121,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5138,11 +5150,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>58.43047714233398</v>
+        <v>58.43048095703125</v>
       </c>
       <c r="C180" t="n">
         <v>63.5099983215332</v>
@@ -5167,11 +5179,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>62.82817840576172</v>
+        <v>62.82818222045898</v>
       </c>
       <c r="C181" t="n">
         <v>68.29000091552734</v>
@@ -5196,11 +5208,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>58.9180908203125</v>
+        <v>58.91809463500977</v>
       </c>
       <c r="C182" t="n">
         <v>64.04000091552734</v>
@@ -5225,7 +5237,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5254,11 +5266,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>61.08951187133789</v>
+        <v>61.08952713012695</v>
       </c>
       <c r="C184" t="n">
         <v>66.15000152587891</v>
@@ -5283,7 +5295,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5312,11 +5324,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>62.59920120239258</v>
+        <v>62.5992317199707</v>
       </c>
       <c r="C186" t="n">
         <v>67.54000091552734</v>
@@ -5341,11 +5353,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>62.48797607421875</v>
+        <v>62.48798370361328</v>
       </c>
       <c r="C187" t="n">
         <v>67.41999816894531</v>
@@ -5370,11 +5382,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>63.77629470825195</v>
+        <v>63.77629089355469</v>
       </c>
       <c r="C188" t="n">
         <v>68.80999755859375</v>
@@ -5399,7 +5411,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5428,11 +5440,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>61.37673568725586</v>
+        <v>61.37675857543945</v>
       </c>
       <c r="C190" t="n">
         <v>65.98000335693359</v>
@@ -5457,11 +5469,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>60.92093658447266</v>
+        <v>60.92092514038086</v>
       </c>
       <c r="C191" t="n">
         <v>65.48999786376953</v>
@@ -5486,11 +5498,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>64.79920196533203</v>
+        <v>64.79920959472656</v>
       </c>
       <c r="C192" t="n">
         <v>69.40000152587891</v>
@@ -5515,11 +5527,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>70.88694763183594</v>
+        <v>70.886962890625</v>
       </c>
       <c r="C193" t="n">
         <v>75.91999816894531</v>
@@ -5544,11 +5556,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>67.19881439208984</v>
+        <v>67.19882202148438</v>
       </c>
       <c r="C194" t="n">
         <v>71.97000122070312</v>
@@ -5573,11 +5585,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>61.94660949707031</v>
+        <v>61.94659805297852</v>
       </c>
       <c r="C195" t="n">
         <v>66.09999847412109</v>
@@ -5602,11 +5614,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>56.77347183227539</v>
+        <v>56.77346038818359</v>
       </c>
       <c r="C196" t="n">
         <v>60.58000183105469</v>
@@ -5631,7 +5643,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5660,7 +5672,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5689,11 +5701,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>52.61685562133789</v>
+        <v>52.61686706542969</v>
       </c>
       <c r="C199" t="n">
         <v>55.84999847412109</v>
@@ -5718,11 +5730,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>57.61946487426758</v>
+        <v>57.61946868896484</v>
       </c>
       <c r="C200" t="n">
         <v>61.15999984741211</v>
@@ -5747,7 +5759,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5776,11 +5788,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.80054092407227</v>
+        <v>58.80054473876953</v>
       </c>
       <c r="C202" t="n">
         <v>62.11999893188477</v>
@@ -5805,11 +5817,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>68.24724578857422</v>
+        <v>68.24725341796875</v>
       </c>
       <c r="C203" t="n">
         <v>72.09999847412109</v>
@@ -5834,11 +5846,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>76.08641052246094</v>
+        <v>76.08641815185547</v>
       </c>
       <c r="C204" t="n">
         <v>80.05000305175781</v>
@@ -5863,11 +5875,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>75.65867614746094</v>
+        <v>75.65869140625</v>
       </c>
       <c r="C205" t="n">
         <v>79.59999847412109</v>
@@ -5892,7 +5904,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5921,11 +5933,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>73.07716369628906</v>
+        <v>73.07717132568359</v>
       </c>
       <c r="C207" t="n">
         <v>76.59999847412109</v>
@@ -5950,11 +5962,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>74.75623321533203</v>
+        <v>74.7562255859375</v>
       </c>
       <c r="C208" t="n">
         <v>78.36000061035156</v>
@@ -5979,11 +5991,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>75.19508361816406</v>
+        <v>75.195068359375</v>
       </c>
       <c r="C209" t="n">
         <v>78.81999969482422</v>
@@ -6008,11 +6020,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>73.57015991210938</v>
+        <v>73.57015228271484</v>
       </c>
       <c r="C210" t="n">
         <v>76.79000091552734</v>
@@ -6037,11 +6049,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>81.23471832275391</v>
+        <v>81.23471069335938</v>
       </c>
       <c r="C211" t="n">
         <v>84.79000091552734</v>
@@ -6066,11 +6078,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>82.90176391601562</v>
+        <v>82.90174865722656</v>
       </c>
       <c r="C212" t="n">
         <v>86.52999877929688</v>
@@ -6095,11 +6107,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>88.94435882568359</v>
+        <v>88.94437408447266</v>
       </c>
       <c r="C213" t="n">
         <v>92.48000335693359</v>
@@ -6124,7 +6136,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6153,11 +6165,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>84.70295715332031</v>
+        <v>84.70297241210938</v>
       </c>
       <c r="C215" t="n">
         <v>88.06999969482422</v>
@@ -6182,11 +6194,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>85.053466796875</v>
+        <v>85.05345916748047</v>
       </c>
       <c r="C216" t="n">
         <v>88.11000061035156</v>
@@ -6211,7 +6223,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6240,7 +6252,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6269,7 +6281,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6298,11 +6310,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>98.23567962646484</v>
+        <v>98.23568725585938</v>
       </c>
       <c r="C220" t="n">
         <v>101.4199981689453</v>
@@ -6327,11 +6339,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>91.13581848144531</v>
+        <v>91.13583374023438</v>
       </c>
       <c r="C221" t="n">
         <v>94.08999633789062</v>
@@ -6356,11 +6368,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>100.2424774169922</v>
+        <v>100.2425003051758</v>
       </c>
       <c r="C222" t="n">
         <v>103.0999984741211</v>
@@ -6385,11 +6397,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>107.0484619140625</v>
+        <v>107.0484771728516</v>
       </c>
       <c r="C223" t="n">
         <v>110.0999984741211</v>
@@ -6414,7 +6426,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6443,11 +6455,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>114.4130783081055</v>
+        <v>114.4130706787109</v>
       </c>
       <c r="C225" t="n">
         <v>117.2699966430664</v>
@@ -6472,11 +6484,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>114.6764984130859</v>
+        <v>114.676513671875</v>
       </c>
       <c r="C226" t="n">
         <v>117.5400009155273</v>
@@ -6501,7 +6513,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6559,11 +6571,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>118.2328567504883</v>
+        <v>118.2328720092773</v>
       </c>
       <c r="C229" t="n">
         <v>120.8099975585938</v>
@@ -6588,11 +6600,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>122.1279754638672</v>
+        <v>122.1279678344727</v>
       </c>
       <c r="C230" t="n">
         <v>124.7900009155273</v>
@@ -6617,11 +6629,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>122.4677581787109</v>
+        <v>122.4677658081055</v>
       </c>
       <c r="C231" t="n">
         <v>124.7600021362305</v>
@@ -6646,11 +6658,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>119.5621337890625</v>
+        <v>119.562141418457</v>
       </c>
       <c r="C232" t="n">
         <v>121.8000030517578</v>
@@ -6675,7 +6687,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6704,11 +6716,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>124.9731140136719</v>
+        <v>124.9731063842773</v>
       </c>
       <c r="C234" t="n">
         <v>126.9000015258789</v>
@@ -6733,7 +6745,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6762,11 +6774,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>122.6390838623047</v>
+        <v>122.6390914916992</v>
       </c>
       <c r="C236" t="n">
         <v>124.5299987792969</v>
@@ -6791,11 +6803,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>134.9634094238281</v>
+        <v>134.9634246826172</v>
       </c>
       <c r="C237" t="n">
         <v>136.6100006103516</v>
@@ -6820,7 +6832,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6849,7 +6861,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6878,7 +6890,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6907,7 +6919,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6936,7 +6948,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6965,7 +6977,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6994,7 +7006,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7023,7 +7035,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7052,7 +7064,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7081,7 +7093,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7110,7 +7122,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7139,7 +7151,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7168,32 +7180,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>131.5899963378906</v>
+        <v>131.6300048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>131.5899963378906</v>
+        <v>131.6300048828125</v>
       </c>
       <c r="D250" t="n">
-        <v>151099500</v>
+        <v>159233300</v>
       </c>
       <c r="E250" t="n">
         <v>5.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24.36851784035012</v>
+        <v>24.37592683015046</v>
       </c>
       <c r="G250" t="n">
         <v>1099974061</v>
       </c>
       <c r="H250" t="n">
-        <v>144745582658.7647</v>
+        <v>144789591020.3971</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1373664210432686</v>
+        <v>0.1447609590495607</v>
       </c>
     </row>
   </sheetData>
@@ -7225,75 +7237,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39565</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39655</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39656</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39746</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7371,13 +7383,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39935</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7413,13 +7425,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39936</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40027</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40208</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="I7" t="n">
         <v>0.7125</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K7" t="n">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I8" t="n">
         <v>0.79</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K8" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40300</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I9" t="n">
         <v>0.8225</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K9" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I10" t="n">
         <v>0.85</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K10" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I11" t="n">
         <v>0.8225</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="K11" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I12" t="n">
         <v>0.79</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="K12" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I13" t="n">
         <v>0.83</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="K13" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I14" t="n">
         <v>0.865</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="K14" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40936</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40995</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I15" t="n">
         <v>0.9675</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40995</v>
       </c>
       <c r="K15" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41027</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I16" t="n">
         <v>1.075</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="K16" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41118</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41145</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I17" t="n">
         <v>1.13</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41145</v>
       </c>
       <c r="K17" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41209</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41242</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I18" t="n">
         <v>1.175</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41242</v>
       </c>
       <c r="K18" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41210</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41307</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41366</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I19" t="n">
         <v>1.275</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41366</v>
       </c>
       <c r="K19" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41308</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41398</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I20" t="n">
         <v>1.31</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="K20" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41399</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41489</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41516</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I21" t="n">
         <v>1.36</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41516</v>
       </c>
       <c r="K21" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41490</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41580</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I22" t="n">
         <v>1.48</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="K22" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41581</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I23" t="n">
         <v>1.475</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="K23" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41672</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41762</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41789</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I24" t="n">
         <v>1.485</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41789</v>
       </c>
       <c r="K24" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41763</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41853</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41880</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I25" t="n">
         <v>1.52</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41880</v>
       </c>
       <c r="K25" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41854</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41975</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I26" t="n">
         <v>1.515</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41975</v>
       </c>
       <c r="K26" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41945</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I27" t="n">
         <v>1.575</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K27" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42126</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I28" t="n">
         <v>1.6</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="K28" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42127</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I29" t="n">
         <v>1.635</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="K29" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42218</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I30" t="n">
         <v>1.64</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="K30" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42399</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42458</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I31" t="n">
         <v>1.67</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42458</v>
       </c>
       <c r="K31" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I32" t="n">
         <v>1.705</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="K32" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42581</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I33" t="n">
         <v>1.725</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="K33" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42672</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I34" t="n">
         <v>1.71</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="K34" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42763</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42822</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I35" t="n">
         <v>1.73</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42822</v>
       </c>
       <c r="K35" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42854</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I36" t="n">
         <v>1.76</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="K36" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42945</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I37" t="n">
         <v>1.765</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="K37" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43036</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43067</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I38" t="n">
         <v>1.85</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43067</v>
       </c>
       <c r="K38" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43134</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43194</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I39" t="n">
         <v>2.02</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43194</v>
       </c>
       <c r="K39" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43135</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43225</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I40" t="n">
         <v>2.175</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="K40" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43226</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43316</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I41" t="n">
         <v>2.335</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="K41" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43317</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43407</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43438</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I42" t="n">
         <v>2.445</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43438</v>
       </c>
       <c r="K42" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43408</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43498</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43558</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I43" t="n">
         <v>2.44</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43558</v>
       </c>
       <c r="K43" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43499</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43589</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I44" t="n">
         <v>2.445</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="K44" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43590</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43680</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I45" t="n">
         <v>2.48</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="K45" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43681</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43771</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43802</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I46" t="n">
         <v>2.55</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43802</v>
       </c>
       <c r="K46" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43772</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I47" t="n">
         <v>2.68</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="K47" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43953</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I48" t="n">
         <v>1.37</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="K48" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I49" t="n">
         <v>0.5700000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="K49" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I50" t="n">
         <v>0.6</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="K50" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44226</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I51" t="n">
         <v>0.05999999999999994</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K51" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I52" t="n">
         <v>1.24</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="K52" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I53" t="n">
         <v>2.06</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="K53" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I54" t="n">
         <v>2.19</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="K54" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I55" t="n">
         <v>2.7</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="K55" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I56" t="n">
         <v>2.75</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="K56" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I57" t="n">
         <v>2.8</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="K57" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I58" t="n">
         <v>2.87</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="K58" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I59" t="n">
         <v>2.97</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="K59" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I60" t="n">
         <v>3.24</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="K60" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45136</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I61" t="n">
         <v>3.4</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="K61" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45227</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I62" t="n">
         <v>3.52</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="K62" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I63" t="n">
         <v>3.86</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="K63" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45326</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45416</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10152,7 +10164,7 @@
       <c r="I64" t="n">
         <v>4.03</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="K64" t="n">
@@ -10165,13 +10177,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45417</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45507</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10198,7 +10210,7 @@
       <c r="I65" t="n">
         <v>4.14</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="K65" t="n">
@@ -10211,13 +10223,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45508</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45598</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10244,7 +10256,7 @@
       <c r="I66" t="n">
         <v>4.25</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="K66" t="n">
@@ -10257,13 +10269,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45599</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10290,7 +10302,7 @@
       <c r="I67" t="n">
         <v>4.26</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="K67" t="n">
@@ -10303,13 +10315,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45690</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45780</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10336,7 +10348,7 @@
       <c r="I68" t="n">
         <v>4.249999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="K68" t="n">
@@ -10349,13 +10361,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45781</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45871</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10382,7 +10394,7 @@
       <c r="I69" t="n">
         <v>4.389999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="K69" t="n">
@@ -10395,13 +10407,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45872</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10428,7 +10440,7 @@
       <c r="I70" t="n">
         <v>4.529999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="K70" t="n">
@@ -10441,13 +10453,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10474,7 +10486,7 @@
       <c r="I71" t="n">
         <v>4.87</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K71" t="n">
@@ -10487,13 +10499,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10520,7 +10532,7 @@
       <c r="I72" t="n">
         <v>5.140000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="K72" t="n">
@@ -10533,13 +10545,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46235</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10566,7 +10578,7 @@
       <c r="I73" t="n">
         <v>5.4</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K73" t="n">
@@ -10603,52 +10615,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="C2" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="C3" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40208</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40267</v>
       </c>
       <c r="C4" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="C5" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="C6" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="C7" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40632</v>
       </c>
       <c r="C8" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="C9" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="C10" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="C11" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40936</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40995</v>
       </c>
       <c r="C12" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41027</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="C13" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41118</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41145</v>
       </c>
       <c r="C14" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41209</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41242</v>
       </c>
       <c r="C15" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41307</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41366</v>
       </c>
       <c r="C16" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41398</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="C17" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41489</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41516</v>
       </c>
       <c r="C18" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41580</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="C19" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="C20" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41762</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41789</v>
       </c>
       <c r="C21" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41853</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41880</v>
       </c>
       <c r="C22" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41975</v>
       </c>
       <c r="C23" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="C24" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42126</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="C25" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="C26" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="C27" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42427</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42458</v>
       </c>
       <c r="C28" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="C29" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42581</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="C30" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42672</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="C31" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42791</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42822</v>
       </c>
       <c r="C32" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42854</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="C33" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42945</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="C34" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43036</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43067</v>
       </c>
       <c r="C35" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43162</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43194</v>
       </c>
       <c r="C36" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43225</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="C37" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43316</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="C38" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43407</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43438</v>
       </c>
       <c r="C39" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43526</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43558</v>
       </c>
       <c r="C40" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43589</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="C41" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43680</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="C42" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43771</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43802</v>
       </c>
       <c r="C43" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="C44" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43953</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="C45" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="C46" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="C47" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44281</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="C48" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44337</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="C49" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44428</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="C50" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44519</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="C51" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44648</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44650</v>
       </c>
       <c r="C52" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44701</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="C53" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44792</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="C54" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44883</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="C55" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45012</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="C56" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45065</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C57" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45156</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="C58" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45247</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="C59" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45373</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="C60" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45436</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="C61" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="C62" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45618</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="C63" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45737</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="C64" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45800</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="C65" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45891</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="C66" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="C67" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="C68" t="n">
@@ -12789,10 +12801,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="C69" t="n">
@@ -12821,10 +12833,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46255</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="C70" t="n">
@@ -12871,12 +12883,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/TJX.xlsx
+++ b/salidas/empresas/TJX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>4.859377861022949</v>
+        <v>4.859379291534424</v>
       </c>
       <c r="C2" t="n">
         <v>6.382500171661377</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>4.672567844390869</v>
+        <v>4.672568798065186</v>
       </c>
       <c r="C3" t="n">
         <v>6.122499942779541</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>4.735528945922852</v>
+        <v>4.73552942276001</v>
       </c>
       <c r="C4" t="n">
         <v>6.204999923706055</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.603882312774658</v>
+        <v>4.603880405426025</v>
       </c>
       <c r="C5" t="n">
         <v>6.03249979019165</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>4.536666393280029</v>
+        <v>4.536667346954346</v>
       </c>
       <c r="C6" t="n">
         <v>5.927499771118164</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>4.37402868270874</v>
+        <v>4.374030590057373</v>
       </c>
       <c r="C7" t="n">
         <v>5.715000152587891</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>4.662955284118652</v>
+        <v>4.662953853607178</v>
       </c>
       <c r="C8" t="n">
         <v>6.09250020980835</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>5.132265090942383</v>
+        <v>5.132266521453857</v>
       </c>
       <c r="C9" t="n">
         <v>6.6875</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>5.377847194671631</v>
+        <v>5.377847671508789</v>
       </c>
       <c r="C10" t="n">
         <v>7.007500171661377</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>5.554358005523682</v>
+        <v>5.55435848236084</v>
       </c>
       <c r="C11" t="n">
         <v>7.237500190734863</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>5.485001564025879</v>
+        <v>5.485002040863037</v>
       </c>
       <c r="C13" t="n">
         <v>7.130000114440918</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>5.686939239501953</v>
+        <v>5.686940670013428</v>
       </c>
       <c r="C14" t="n">
         <v>7.392499923706055</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>5.302038192749023</v>
+        <v>5.302036762237549</v>
       </c>
       <c r="C15" t="n">
         <v>6.875</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>5.197924613952637</v>
+        <v>5.197925090789795</v>
       </c>
       <c r="C16" t="n">
         <v>6.739999771118164</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>5.377232074737549</v>
+        <v>5.377230167388916</v>
       </c>
       <c r="C17" t="n">
         <v>6.972499847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>5.409901142120361</v>
+        <v>5.409903526306152</v>
       </c>
       <c r="C18" t="n">
         <v>6.992499828338623</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>5.318996429443359</v>
+        <v>5.318996906280518</v>
       </c>
       <c r="C19" t="n">
         <v>6.875</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>5.367351055145264</v>
+        <v>5.367348670959473</v>
       </c>
       <c r="C20" t="n">
         <v>6.9375</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>5.916142463684082</v>
+        <v>5.916143894195557</v>
       </c>
       <c r="C21" t="n">
         <v>7.622499942779541</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>5.640609741210938</v>
+        <v>5.640610694885254</v>
       </c>
       <c r="C22" t="n">
         <v>7.267499923706055</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>5.613448619842529</v>
+        <v>5.613449573516846</v>
       </c>
       <c r="C23" t="n">
         <v>7.232500076293945</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>5.711742401123047</v>
+        <v>5.71174430847168</v>
       </c>
       <c r="C24" t="n">
         <v>7.335000038146973</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>6.247459411621094</v>
+        <v>6.247460842132568</v>
       </c>
       <c r="C27" t="n">
         <v>8</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>6.290413856506348</v>
+        <v>6.290411949157715</v>
       </c>
       <c r="C29" t="n">
         <v>8.055000305175781</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>6.281141757965088</v>
+        <v>6.281144618988037</v>
       </c>
       <c r="C30" t="n">
         <v>8.015000343322754</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.604409217834473</v>
+        <v>6.60440731048584</v>
       </c>
       <c r="C32" t="n">
         <v>8.427499771118164</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>7.123486042022705</v>
+        <v>7.123482704162598</v>
       </c>
       <c r="C33" t="n">
         <v>9.060000419616699</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>5.999131202697754</v>
+        <v>5.99913501739502</v>
       </c>
       <c r="C34" t="n">
         <v>7.630000114440918</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.26005220413208</v>
+        <v>5.260052680969238</v>
       </c>
       <c r="C35" t="n">
         <v>6.690000057220459</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>4.504649639129639</v>
+        <v>4.504646778106689</v>
       </c>
       <c r="C36" t="n">
         <v>5.704999923706055</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>4.060499668121338</v>
+        <v>4.060500621795654</v>
       </c>
       <c r="C37" t="n">
         <v>5.142499923706055</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>3.833489894866943</v>
+        <v>3.833491086959839</v>
       </c>
       <c r="C38" t="n">
         <v>4.855000019073486</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>4.417678833007812</v>
+        <v>4.417677402496338</v>
       </c>
       <c r="C39" t="n">
         <v>5.567500114440918</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>5.086181640625</v>
+        <v>5.086179256439209</v>
       </c>
       <c r="C40" t="n">
         <v>6.409999847412109</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.548378944396973</v>
+        <v>5.548379421234131</v>
       </c>
       <c r="C41" t="n">
         <v>6.992499828338623</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>6.267694473266602</v>
+        <v>6.267693519592285</v>
       </c>
       <c r="C43" t="n">
         <v>7.864999771118164</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>7.218009948730469</v>
+        <v>7.218013286590576</v>
       </c>
       <c r="C44" t="n">
         <v>9.057499885559082</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.186747550964355</v>
+        <v>7.186744213104248</v>
       </c>
       <c r="C45" t="n">
         <v>8.987500190734863</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.426637172698975</v>
+        <v>7.426644802093506</v>
       </c>
       <c r="C46" t="n">
         <v>9.287500381469727</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.466619491577148</v>
+        <v>7.466618061065674</v>
       </c>
       <c r="C47" t="n">
         <v>9.337499618530273</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.696622848510742</v>
+        <v>7.696620941162109</v>
       </c>
       <c r="C48" t="n">
         <v>9.595000267028809</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.622422695159912</v>
+        <v>7.622421741485596</v>
       </c>
       <c r="C50" t="n">
         <v>9.502499580383301</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.374961853027344</v>
+        <v>8.374964714050293</v>
       </c>
       <c r="C51" t="n">
         <v>10.40750026702881</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>8.554008483886719</v>
+        <v>8.554011344909668</v>
       </c>
       <c r="C52" t="n">
         <v>10.63000011444092</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>9.322503089904785</v>
+        <v>9.322502136230469</v>
       </c>
       <c r="C53" t="n">
         <v>11.58500003814697</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>9.175545692443848</v>
+        <v>9.175546646118164</v>
       </c>
       <c r="C54" t="n">
         <v>11.36499977111816</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>8.467098236083984</v>
+        <v>8.467093467712402</v>
       </c>
       <c r="C55" t="n">
         <v>10.48750019073486</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.380302429199219</v>
+        <v>8.380304336547852</v>
       </c>
       <c r="C56" t="n">
         <v>10.38000011444092</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.038998603820801</v>
+        <v>8.038997650146484</v>
       </c>
       <c r="C57" t="n">
         <v>9.922499656677246</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.267580986022949</v>
+        <v>9.267582893371582</v>
       </c>
       <c r="C60" t="n">
         <v>11.40250015258789</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>9.019686698913574</v>
+        <v>9.019681930541992</v>
       </c>
       <c r="C61" t="n">
         <v>11.09749984741211</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>9.629262924194336</v>
+        <v>9.62926197052002</v>
       </c>
       <c r="C62" t="n">
         <v>11.84749984741211</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.1352653503418</v>
+        <v>10.13527011871338</v>
       </c>
       <c r="C64" t="n">
         <v>12.43249988555908</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.92806911468506</v>
+        <v>10.92806816101074</v>
       </c>
       <c r="C65" t="n">
         <v>13.40499973297119</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.84455013275146</v>
+        <v>10.84454536437988</v>
       </c>
       <c r="C66" t="n">
         <v>13.25500011444092</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>11.31088829040527</v>
+        <v>11.31089210510254</v>
       </c>
       <c r="C68" t="n">
         <v>13.82499980926514</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>11.38828086853027</v>
+        <v>11.38828277587891</v>
       </c>
       <c r="C70" t="n">
         <v>13.86750030517578</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.09863567352295</v>
+        <v>12.09864139556885</v>
       </c>
       <c r="C71" t="n">
         <v>14.73250007629395</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.70719051361084</v>
+        <v>12.70718669891357</v>
       </c>
       <c r="C72" t="n">
         <v>15.42500019073486</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>13.29415130615234</v>
+        <v>13.29415225982666</v>
       </c>
       <c r="C73" t="n">
         <v>16.13750076293945</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>14.0335168838501</v>
+        <v>14.03351402282715</v>
       </c>
       <c r="C74" t="n">
         <v>17.03499984741211</v>
@@ -2138,7 +2138,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>16.40204620361328</v>
+        <v>16.40204811096191</v>
       </c>
       <c r="C76" t="n">
         <v>19.85499954223633</v>
@@ -2167,7 +2167,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>17.22813606262207</v>
+        <v>17.2281379699707</v>
       </c>
       <c r="C77" t="n">
         <v>20.85499954223633</v>
@@ -2196,7 +2196,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.58666801452637</v>
+        <v>17.586669921875</v>
       </c>
       <c r="C78" t="n">
         <v>21.22999954223633</v>
@@ -2225,7 +2225,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.78134536743164</v>
+        <v>17.78134155273438</v>
       </c>
       <c r="C79" t="n">
         <v>21.46500015258789</v>
@@ -2254,7 +2254,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.34049987792969</v>
+        <v>18.34049415588379</v>
       </c>
       <c r="C80" t="n">
         <v>22.13999938964844</v>
@@ -2283,7 +2283,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>19.01425170898438</v>
+        <v>19.01425743103027</v>
       </c>
       <c r="C81" t="n">
         <v>22.89500045776367</v>
@@ -2312,7 +2312,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>18.59900665283203</v>
+        <v>18.5990104675293</v>
       </c>
       <c r="C82" t="n">
         <v>22.39500045776367</v>
@@ -2341,7 +2341,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.28682136535645</v>
+        <v>17.28682518005371</v>
       </c>
       <c r="C83" t="n">
         <v>20.81500053405762</v>
@@ -2370,7 +2370,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>18.46271133422852</v>
+        <v>18.46270942687988</v>
       </c>
       <c r="C84" t="n">
         <v>22.17000007629395</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.67572975158691</v>
+        <v>17.67573165893555</v>
       </c>
       <c r="C85" t="n">
         <v>21.22500038146973</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>18.81247711181641</v>
+        <v>18.81247329711914</v>
       </c>
       <c r="C86" t="n">
         <v>22.59000015258789</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.77259254455566</v>
+        <v>18.77258682250977</v>
       </c>
       <c r="C87" t="n">
         <v>22.48500061035156</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>19.51564025878906</v>
+        <v>19.51564407348633</v>
       </c>
       <c r="C88" t="n">
         <v>23.375</v>
@@ -2515,7 +2515,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.35888290405273</v>
+        <v>20.35888671875</v>
       </c>
       <c r="C89" t="n">
         <v>24.38500022888184</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>21.1876335144043</v>
+        <v>21.18764305114746</v>
       </c>
       <c r="C90" t="n">
         <v>25.30500030517578</v>
@@ -2573,7 +2573,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>20.95739364624023</v>
+        <v>20.95738983154297</v>
       </c>
       <c r="C91" t="n">
         <v>25.03000068664551</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>21.78630065917969</v>
+        <v>21.78630447387695</v>
       </c>
       <c r="C92" t="n">
         <v>26.02000045776367</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>22.13222694396973</v>
+        <v>22.13223075866699</v>
       </c>
       <c r="C93" t="n">
         <v>26.36000061035156</v>
@@ -2660,7 +2660,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>23.67291831970215</v>
+        <v>23.67292404174805</v>
       </c>
       <c r="C94" t="n">
         <v>28.19499969482422</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>25.52006912231445</v>
+        <v>25.52007293701172</v>
       </c>
       <c r="C95" t="n">
         <v>30.39500045776367</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>26.45966339111328</v>
+        <v>26.45966148376465</v>
       </c>
       <c r="C96" t="n">
         <v>31.44000053405762</v>
@@ -2747,7 +2747,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>26.81733894348145</v>
+        <v>26.81732940673828</v>
       </c>
       <c r="C97" t="n">
         <v>31.86499977111816</v>
@@ -2776,7 +2776,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>24.13686943054199</v>
+        <v>24.13686752319336</v>
       </c>
       <c r="C98" t="n">
         <v>28.68000030517578</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>25.92555999755859</v>
+        <v>25.92556381225586</v>
       </c>
       <c r="C99" t="n">
         <v>30.72999954223633</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>25.58388137817383</v>
+        <v>25.58389091491699</v>
       </c>
       <c r="C100" t="n">
         <v>30.32500076293945</v>
@@ -2863,7 +2863,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>24.54197120666504</v>
+        <v>24.54197692871094</v>
       </c>
       <c r="C101" t="n">
         <v>29.09000015258789</v>
@@ -2892,7 +2892,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>23.03589630126953</v>
+        <v>23.0358943939209</v>
       </c>
       <c r="C102" t="n">
         <v>27.22500038146973</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>22.48591613769531</v>
+        <v>22.48591232299805</v>
       </c>
       <c r="C103" t="n">
         <v>26.57500076293945</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>25.30021286010742</v>
+        <v>25.30020523071289</v>
       </c>
       <c r="C105" t="n">
         <v>29.80500030517578</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>25.11346435546875</v>
+        <v>25.11346244812012</v>
       </c>
       <c r="C106" t="n">
         <v>29.58499908447266</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>28.15720748901367</v>
+        <v>28.1572093963623</v>
       </c>
       <c r="C108" t="n">
         <v>33.08000183105469</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>29.1871509552002</v>
+        <v>29.18714141845703</v>
       </c>
       <c r="C109" t="n">
         <v>34.29000091552734</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>28.06357955932617</v>
+        <v>28.06358337402344</v>
       </c>
       <c r="C110" t="n">
         <v>32.97000122070312</v>
@@ -3153,7 +3153,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.28861808776855</v>
+        <v>29.28861236572266</v>
       </c>
       <c r="C111" t="n">
         <v>34.31999969482422</v>
@@ -3182,7 +3182,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>29.89025497436523</v>
+        <v>29.89025115966797</v>
       </c>
       <c r="C112" t="n">
         <v>35.02500152587891</v>
@@ -3211,7 +3211,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.53915023803711</v>
+        <v>27.53914642333984</v>
       </c>
       <c r="C113" t="n">
         <v>32.27000045776367</v>
@@ -3240,7 +3240,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>27.55745506286621</v>
+        <v>27.55745697021484</v>
       </c>
       <c r="C114" t="n">
         <v>32.18999862670898</v>
@@ -3269,7 +3269,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>28.32364654541016</v>
+        <v>28.32365226745605</v>
       </c>
       <c r="C115" t="n">
         <v>33.08499908447266</v>
@@ -3327,7 +3327,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>30.19038391113281</v>
+        <v>30.19038200378418</v>
       </c>
       <c r="C117" t="n">
         <v>35.15999984741211</v>
@@ -3356,7 +3356,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>30.66264343261719</v>
+        <v>30.66265106201172</v>
       </c>
       <c r="C118" t="n">
         <v>35.70999908447266</v>
@@ -3385,7 +3385,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.42255020141602</v>
+        <v>31.42255592346191</v>
       </c>
       <c r="C119" t="n">
         <v>36.59500122070312</v>
@@ -3414,7 +3414,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>30.39813232421875</v>
+        <v>30.39813041687012</v>
       </c>
       <c r="C120" t="n">
         <v>35.29999923706055</v>
@@ -3443,7 +3443,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>30.53160095214844</v>
+        <v>30.53161239624023</v>
       </c>
       <c r="C121" t="n">
         <v>35.45500183105469</v>
@@ -3472,7 +3472,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>30.67369079589844</v>
+        <v>30.67369270324707</v>
       </c>
       <c r="C122" t="n">
         <v>35.61999893188477</v>
@@ -3501,7 +3501,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>32.00392532348633</v>
+        <v>32.00392913818359</v>
       </c>
       <c r="C123" t="n">
         <v>37.04999923706055</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.74679946899414</v>
+        <v>32.74681091308594</v>
       </c>
       <c r="C125" t="n">
         <v>37.90999984741211</v>
@@ -3588,7 +3588,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.98664474487305</v>
+        <v>32.98664093017578</v>
       </c>
       <c r="C126" t="n">
         <v>38.06000137329102</v>
@@ -3617,7 +3617,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>33.46764755249023</v>
+        <v>33.46765518188477</v>
       </c>
       <c r="C127" t="n">
         <v>38.6150016784668</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.41340637207031</v>
+        <v>35.41339111328125</v>
       </c>
       <c r="C128" t="n">
         <v>40.86000061035156</v>
@@ -3675,7 +3675,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>33.66595840454102</v>
+        <v>33.66595458984375</v>
       </c>
       <c r="C129" t="n">
         <v>38.72000122070312</v>
@@ -3704,7 +3704,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>32.50955200195312</v>
+        <v>32.50955581665039</v>
       </c>
       <c r="C130" t="n">
         <v>37.38999938964844</v>
@@ -3733,7 +3733,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>32.06177139282227</v>
+        <v>32.06178665161133</v>
       </c>
       <c r="C131" t="n">
         <v>36.875</v>
@@ -3762,7 +3762,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>34.17839431762695</v>
+        <v>34.17839813232422</v>
       </c>
       <c r="C132" t="n">
         <v>39.16999816894531</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>32.77793884277344</v>
+        <v>32.77793502807617</v>
       </c>
       <c r="C133" t="n">
         <v>37.56499862670898</v>
@@ -3820,7 +3820,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>32.68630981445312</v>
+        <v>32.68631744384766</v>
       </c>
       <c r="C134" t="n">
         <v>37.45999908447266</v>
@@ -3849,7 +3849,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>34.34492492675781</v>
+        <v>34.34493255615234</v>
       </c>
       <c r="C135" t="n">
         <v>39.22499847412109</v>
@@ -3878,7 +3878,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>34.62074661254883</v>
+        <v>34.6207389831543</v>
       </c>
       <c r="C136" t="n">
         <v>39.54000091552734</v>
@@ -3907,7 +3907,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>34.42811584472656</v>
+        <v>34.4281120300293</v>
       </c>
       <c r="C137" t="n">
         <v>39.31999969482422</v>
@@ -3965,7 +3965,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>31.72206878662109</v>
+        <v>31.72207641601562</v>
       </c>
       <c r="C139" t="n">
         <v>36.08499908447266</v>
@@ -3994,7 +3994,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>30.90451431274414</v>
+        <v>30.9045238494873</v>
       </c>
       <c r="C140" t="n">
         <v>35.15499877929688</v>
@@ -4023,7 +4023,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.92057418823242</v>
+        <v>31.92057228088379</v>
       </c>
       <c r="C141" t="n">
         <v>36.15000152587891</v>
@@ -4052,7 +4052,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>32.55192565917969</v>
+        <v>32.55191040039062</v>
       </c>
       <c r="C142" t="n">
         <v>36.8650016784668</v>
@@ -4081,7 +4081,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>30.81682586669922</v>
+        <v>30.81681060791016</v>
       </c>
       <c r="C143" t="n">
         <v>34.90000152587891</v>
@@ -4110,7 +4110,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>33.50901031494141</v>
+        <v>33.50900650024414</v>
       </c>
       <c r="C144" t="n">
         <v>37.77500152587891</v>
@@ -4139,7 +4139,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>33.91262435913086</v>
+        <v>33.91262817382812</v>
       </c>
       <c r="C145" t="n">
         <v>38.22999954223633</v>
@@ -4168,7 +4168,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>35.62466812133789</v>
+        <v>35.62467193603516</v>
       </c>
       <c r="C146" t="n">
         <v>40.15999984741211</v>
@@ -4197,7 +4197,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>36.82397842407227</v>
+        <v>36.82397079467773</v>
       </c>
       <c r="C147" t="n">
         <v>41.34000015258789</v>
@@ -4226,7 +4226,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>36.32515335083008</v>
+        <v>36.32514572143555</v>
       </c>
       <c r="C148" t="n">
         <v>40.77999877929688</v>
@@ -4255,7 +4255,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>37.79045104980469</v>
+        <v>37.79044723510742</v>
       </c>
       <c r="C149" t="n">
         <v>42.42499923706055</v>
@@ -4284,7 +4284,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>40.41080474853516</v>
+        <v>40.41079711914062</v>
       </c>
       <c r="C150" t="n">
         <v>45.15999984741211</v>
@@ -4313,7 +4313,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.58525848388672</v>
+        <v>42.58524703979492</v>
       </c>
       <c r="C151" t="n">
         <v>47.59000015258789</v>
@@ -4371,7 +4371,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>49.39329528808594</v>
+        <v>49.39328765869141</v>
       </c>
       <c r="C153" t="n">
         <v>54.98500061035156</v>
@@ -4400,7 +4400,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>50.31404876708984</v>
+        <v>50.31406402587891</v>
       </c>
       <c r="C154" t="n">
         <v>56.0099983215332</v>
@@ -4429,7 +4429,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>49.35286712646484</v>
+        <v>49.35287094116211</v>
       </c>
       <c r="C155" t="n">
         <v>54.93999862670898</v>
@@ -4458,7 +4458,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>44.04196548461914</v>
+        <v>44.04196929931641</v>
       </c>
       <c r="C156" t="n">
         <v>48.84999847412109</v>
@@ -4516,7 +4516,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>44.83536911010742</v>
+        <v>44.83536148071289</v>
       </c>
       <c r="C158" t="n">
         <v>49.72999954223633</v>
@@ -4545,7 +4545,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>46.42378616333008</v>
+        <v>46.42378997802734</v>
       </c>
       <c r="C159" t="n">
         <v>51.29000091552734</v>
@@ -4574,7 +4574,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.16162109375</v>
+        <v>48.1616096496582</v>
       </c>
       <c r="C160" t="n">
         <v>53.20999908447266</v>
@@ -4661,7 +4661,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>48.07320785522461</v>
+        <v>48.07321548461914</v>
       </c>
       <c r="C163" t="n">
         <v>52.88000106811523</v>
@@ -4719,7 +4719,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.18883514404297</v>
+        <v>50.1888313293457</v>
       </c>
       <c r="C165" t="n">
         <v>54.97000122070312</v>
@@ -4748,7 +4748,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>50.89186859130859</v>
+        <v>50.89186096191406</v>
       </c>
       <c r="C166" t="n">
         <v>55.7400016784668</v>
@@ -4835,7 +4835,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>55.96956634521484</v>
+        <v>55.96957778930664</v>
       </c>
       <c r="C169" t="n">
         <v>61.06000137329102</v>
@@ -4864,7 +4864,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.11798095703125</v>
+        <v>54.11797714233398</v>
       </c>
       <c r="C170" t="n">
         <v>59.04000091552734</v>
@@ -4893,7 +4893,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>55.01720809936523</v>
+        <v>55.01720428466797</v>
       </c>
       <c r="C171" t="n">
         <v>59.79999923706055</v>
@@ -4922,7 +4922,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>43.98617553710938</v>
+        <v>43.98616409301758</v>
       </c>
       <c r="C172" t="n">
         <v>47.81000137329102</v>
@@ -4951,7 +4951,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>45.12698364257812</v>
+        <v>45.12699127197266</v>
       </c>
       <c r="C173" t="n">
         <v>49.04999923706055</v>
@@ -4980,7 +4980,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>48.54026412963867</v>
+        <v>48.54026794433594</v>
       </c>
       <c r="C174" t="n">
         <v>52.7599983215332</v>
@@ -5009,7 +5009,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>46.5162239074707</v>
+        <v>46.51622009277344</v>
       </c>
       <c r="C175" t="n">
         <v>50.56000137329102</v>
@@ -5067,7 +5067,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>50.40790939331055</v>
+        <v>50.40790557861328</v>
       </c>
       <c r="C177" t="n">
         <v>54.79000091552734</v>
@@ -5096,7 +5096,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>51.19911956787109</v>
+        <v>51.19912338256836</v>
       </c>
       <c r="C178" t="n">
         <v>55.65000152587891</v>
@@ -5125,7 +5125,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.73702239990234</v>
+        <v>46.73702621459961</v>
       </c>
       <c r="C179" t="n">
         <v>50.79999923706055</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>62.82818222045898</v>
+        <v>62.82818984985352</v>
       </c>
       <c r="C181" t="n">
         <v>68.29000091552734</v>
@@ -5212,7 +5212,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>58.91809463500977</v>
+        <v>58.91809844970703</v>
       </c>
       <c r="C182" t="n">
         <v>64.04000091552734</v>
@@ -5241,7 +5241,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>60.94176483154297</v>
+        <v>60.9417610168457</v>
       </c>
       <c r="C183" t="n">
         <v>65.98999786376953</v>
@@ -5299,7 +5299,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>65.56849670410156</v>
+        <v>65.56851196289062</v>
       </c>
       <c r="C185" t="n">
         <v>71</v>
@@ -5328,7 +5328,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>62.5992317199707</v>
+        <v>62.59921646118164</v>
       </c>
       <c r="C186" t="n">
         <v>67.54000091552734</v>
@@ -5357,7 +5357,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>62.48798370361328</v>
+        <v>62.48799514770508</v>
       </c>
       <c r="C187" t="n">
         <v>67.41999816894531</v>
@@ -5386,7 +5386,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>63.77629089355469</v>
+        <v>63.77630615234375</v>
       </c>
       <c r="C188" t="n">
         <v>68.80999755859375</v>
@@ -5415,7 +5415,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>67.64649200439453</v>
+        <v>67.64651489257812</v>
       </c>
       <c r="C189" t="n">
         <v>72.72000122070312</v>
@@ -5444,7 +5444,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>61.37675857543945</v>
+        <v>61.37673950195312</v>
       </c>
       <c r="C190" t="n">
         <v>65.98000335693359</v>
@@ -5502,7 +5502,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>64.79920959472656</v>
+        <v>64.79921722412109</v>
       </c>
       <c r="C192" t="n">
         <v>69.40000152587891</v>
@@ -5531,7 +5531,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>70.886962890625</v>
+        <v>70.88697052001953</v>
       </c>
       <c r="C193" t="n">
         <v>75.91999816894531</v>
@@ -5589,7 +5589,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>61.94659805297852</v>
+        <v>61.94661331176758</v>
       </c>
       <c r="C195" t="n">
         <v>66.09999847412109</v>
@@ -5618,7 +5618,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>56.77346038818359</v>
+        <v>56.77346420288086</v>
       </c>
       <c r="C196" t="n">
         <v>60.58000183105469</v>
@@ -5647,7 +5647,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>57.42948150634766</v>
+        <v>57.42947387695312</v>
       </c>
       <c r="C197" t="n">
         <v>61.27999877929688</v>
@@ -5676,7 +5676,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>59.88995361328125</v>
+        <v>59.88995742797852</v>
       </c>
       <c r="C198" t="n">
         <v>63.56999969482422</v>
@@ -5705,7 +5705,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>52.61686706542969</v>
+        <v>52.61685943603516</v>
       </c>
       <c r="C199" t="n">
         <v>55.84999847412109</v>
@@ -5734,7 +5734,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>57.61946868896484</v>
+        <v>57.61947250366211</v>
       </c>
       <c r="C200" t="n">
         <v>61.15999984741211</v>
@@ -5763,7 +5763,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>59.01825714111328</v>
+        <v>59.01826095581055</v>
       </c>
       <c r="C201" t="n">
         <v>62.34999847412109</v>
@@ -5821,7 +5821,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>68.24725341796875</v>
+        <v>68.24726104736328</v>
       </c>
       <c r="C203" t="n">
         <v>72.09999847412109</v>
@@ -5850,7 +5850,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>76.08641815185547</v>
+        <v>76.08641052246094</v>
       </c>
       <c r="C204" t="n">
         <v>80.05000305175781</v>
@@ -5908,7 +5908,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>77.80678558349609</v>
+        <v>77.80677795410156</v>
       </c>
       <c r="C206" t="n">
         <v>81.86000061035156</v>
@@ -5995,7 +5995,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>75.195068359375</v>
+        <v>75.19507598876953</v>
       </c>
       <c r="C209" t="n">
         <v>78.81999969482422</v>
@@ -6024,7 +6024,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>73.57015228271484</v>
+        <v>73.57015991210938</v>
       </c>
       <c r="C210" t="n">
         <v>76.79000091552734</v>
@@ -6111,7 +6111,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>88.94437408447266</v>
+        <v>88.94436645507812</v>
       </c>
       <c r="C213" t="n">
         <v>92.48000335693359</v>
@@ -6140,7 +6140,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>85.48200225830078</v>
+        <v>85.48199462890625</v>
       </c>
       <c r="C214" t="n">
         <v>88.87999725341797</v>
@@ -6285,7 +6285,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>96.02727508544922</v>
+        <v>96.02726745605469</v>
       </c>
       <c r="C219" t="n">
         <v>99.13999938964844</v>
@@ -6343,7 +6343,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>91.13583374023438</v>
+        <v>91.13581085205078</v>
       </c>
       <c r="C221" t="n">
         <v>94.08999633789062</v>
@@ -6372,7 +6372,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>100.2425003051758</v>
+        <v>100.2424850463867</v>
       </c>
       <c r="C222" t="n">
         <v>103.0999984741211</v>
@@ -6401,7 +6401,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>107.0484771728516</v>
+        <v>107.048469543457</v>
       </c>
       <c r="C223" t="n">
         <v>110.0999984741211</v>
@@ -6430,7 +6430,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>109.8875427246094</v>
+        <v>109.8875350952148</v>
       </c>
       <c r="C224" t="n">
         <v>113.0199966430664</v>
@@ -6488,7 +6488,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>114.676513671875</v>
+        <v>114.6765060424805</v>
       </c>
       <c r="C226" t="n">
         <v>117.5400009155273</v>
@@ -6517,7 +6517,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>110.2763824462891</v>
+        <v>110.2763671875</v>
       </c>
       <c r="C227" t="n">
         <v>113.0299987792969</v>
@@ -6546,7 +6546,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>123.0087738037109</v>
+        <v>123.0087814331055</v>
       </c>
       <c r="C228" t="n">
         <v>125.6900024414062</v>
@@ -6633,7 +6633,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>122.4677658081055</v>
+        <v>122.4677581787109</v>
       </c>
       <c r="C231" t="n">
         <v>124.7600021362305</v>
@@ -6778,7 +6778,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>122.6390914916992</v>
+        <v>122.6390991210938</v>
       </c>
       <c r="C236" t="n">
         <v>124.5299987792969</v>
@@ -6807,7 +6807,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>134.9634246826172</v>
+        <v>134.9633941650391</v>
       </c>
       <c r="C237" t="n">
         <v>136.6100006103516</v>
@@ -6836,7 +6836,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>142.7978210449219</v>
+        <v>142.7978057861328</v>
       </c>
       <c r="C238" t="n">
         <v>144.5399932861328</v>
@@ -6952,7 +6952,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>148.4316253662109</v>
+        <v>148.4316101074219</v>
       </c>
       <c r="C242" t="n">
         <v>149.8099975585938</v>
@@ -7010,7 +7010,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>158.6779632568359</v>
+        <v>158.677978515625</v>
       </c>
       <c r="C244" t="n">
         <v>159.6999969482422</v>
@@ -7039,7 +7039,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>155.7468414306641</v>
+        <v>155.7468566894531</v>
       </c>
       <c r="C245" t="n">
         <v>156.75</v>
